--- a/tests/systeem_testen/224/results/df_beta_scenarios.xlsx
+++ b/tests/systeem_testen/224/results/df_beta_scenarios.xlsx
@@ -484,14 +484,14 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.84</v>
+        <v>27.89</v>
       </c>
       <c r="G2" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.738223270312046e-171</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.54, 20.84, 2.44</t>
         </is>
       </c>
     </row>
@@ -514,14 +514,14 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>9.84</v>
+        <v>27.41</v>
       </c>
       <c r="G3" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.678598680257558e-166</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.46, 20.54, 2.2</t>
         </is>
       </c>
     </row>
@@ -544,14 +544,14 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9.84</v>
+        <v>16.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.469947485489923e-65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>14.65, 16.44, 0.66</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>9.84</v>
+        <v>14.27</v>
       </c>
       <c r="G5" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.570490951438946e-46</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.83, 14.09, -0.82</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>9.84</v>
+        <v>26.23</v>
       </c>
       <c r="G6" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.589611861524541e-152</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.25, 19.78, 1.67</t>
         </is>
       </c>
     </row>
@@ -634,14 +634,14 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>9.84</v>
+        <v>27.12</v>
       </c>
       <c r="G7" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.749918415221198e-162</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.41, 20.37, 1.97</t>
         </is>
       </c>
     </row>
@@ -664,14 +664,14 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>9.84</v>
+        <v>27.16</v>
       </c>
       <c r="G8" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.048642943733701e-162</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.41, 20.39, 1.99</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9.84</v>
+        <v>17.28</v>
       </c>
       <c r="G9" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.291231350136076e-67</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>14.8, 16.67, 0.91</t>
         </is>
       </c>
     </row>
@@ -724,14 +724,14 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9.84</v>
+        <v>26.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.511962590025216e-154</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.28, 19.89, 1.73</t>
         </is>
       </c>
     </row>
@@ -754,14 +754,14 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9.84</v>
+        <v>28.07</v>
       </c>
       <c r="G11" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.031643010433468e-173</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.55, 20.95, 2.69</t>
         </is>
       </c>
     </row>
@@ -784,14 +784,14 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>9.84</v>
+        <v>27.93</v>
       </c>
       <c r="G12" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.531433836387407e-172</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.53, 20.84, 2.77</t>
         </is>
       </c>
     </row>
@@ -814,14 +814,14 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>9.84</v>
+        <v>26.65</v>
       </c>
       <c r="G13" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.880607156402828e-157</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.32, 20.06, 1.81</t>
         </is>
       </c>
     </row>
@@ -844,14 +844,14 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>9.84</v>
+        <v>27.11</v>
       </c>
       <c r="G14" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.90265286812219e-162</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.39, 20.34, 2.52</t>
         </is>
       </c>
     </row>
@@ -874,14 +874,14 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>9.84</v>
+        <v>27.16</v>
       </c>
       <c r="G15" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.317140309120556e-163</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.4, 20.36, 2.59</t>
         </is>
       </c>
     </row>
@@ -904,14 +904,14 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>9.84</v>
+        <v>25.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.519499775138432e-148</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.19, 19.63, 1.95</t>
         </is>
       </c>
     </row>
@@ -934,14 +934,14 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>9.84</v>
+        <v>25.68</v>
       </c>
       <c r="G17" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.031820710408866e-145</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.16, 19.52, 1.52</t>
         </is>
       </c>
     </row>
@@ -964,14 +964,14 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>9.84</v>
+        <v>25.83</v>
       </c>
       <c r="G18" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.967711496830981e-147</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.17, 19.58, 2.01</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>9.84</v>
+        <v>25.33</v>
       </c>
       <c r="G19" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.446515874180643e-142</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.07, 19.27, 2.16</t>
         </is>
       </c>
     </row>
@@ -1024,14 +1024,14 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>9.84</v>
+        <v>13.96</v>
       </c>
       <c r="G20" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.307438727690809e-44</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.58, 13.8, -0.69</t>
         </is>
       </c>
     </row>
@@ -1054,14 +1054,14 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>9.84</v>
+        <v>13.92</v>
       </c>
       <c r="G21" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.410106294400354e-44</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.52, 13.73, -0.2</t>
         </is>
       </c>
     </row>
@@ -1084,14 +1084,14 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>9.84</v>
+        <v>14.88</v>
       </c>
       <c r="G22" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.069663694866074e-50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>13.29, 14.68, -1.41</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1114,14 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>9.84</v>
+        <v>23.01</v>
       </c>
       <c r="G23" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.759154632781997e-117</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.21, 20.04, 2.66</t>
         </is>
       </c>
     </row>
@@ -1144,14 +1144,14 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>9.84</v>
+        <v>26.62</v>
       </c>
       <c r="G24" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.864389528898285e-156</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.25, 20.17, 2.68</t>
         </is>
       </c>
     </row>
@@ -1174,14 +1174,14 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>9.84</v>
+        <v>33.48</v>
       </c>
       <c r="G25" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.865081137474357e-246</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>17.19, 24.71, 5.23</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1204,14 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>9.84</v>
+        <v>14.84</v>
       </c>
       <c r="G26" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.832427691087692e-50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>13.22, 14.63, -1.12</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1234,14 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>9.84</v>
+        <v>14.37</v>
       </c>
       <c r="G27" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.15448804624222e-47</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.84, 14.16, -1.86</t>
         </is>
       </c>
     </row>
@@ -1264,14 +1264,14 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>9.84</v>
+        <v>14.13</v>
       </c>
       <c r="G28" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.319149914024955e-45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.63, 13.91, -2.29</t>
         </is>
       </c>
     </row>
@@ -1294,14 +1294,14 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>9.84</v>
+        <v>14.3</v>
       </c>
       <c r="G29" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.023410930530316e-46</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.8, 14.12, -0.43</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1324,14 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>9.84</v>
+        <v>13.28</v>
       </c>
       <c r="G30" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.46268743978562e-40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>11.96, 13.12, -1.84</t>
         </is>
       </c>
     </row>
@@ -1354,14 +1354,14 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>9.84</v>
+        <v>13.36</v>
       </c>
       <c r="G31" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.164919137477e-41</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>11.94, 13.1, -3.44</t>
         </is>
       </c>
     </row>
@@ -1384,14 +1384,14 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>9.84</v>
+        <v>14.09</v>
       </c>
       <c r="G32" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.185003069200744e-45</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.04, 13.22, -6.21</t>
         </is>
       </c>
     </row>
@@ -1414,14 +1414,14 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>9.84</v>
+        <v>15.44</v>
       </c>
       <c r="G33" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.093293593845343e-54</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>11.92, 13.07, -9.21</t>
         </is>
       </c>
     </row>
@@ -1444,14 +1444,14 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>9.84</v>
+        <v>13.76</v>
       </c>
       <c r="G34" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.201012675825945e-43</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>11.9, 13.05, -5.8</t>
         </is>
       </c>
     </row>
@@ -1474,14 +1474,14 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>9.84</v>
+        <v>13.39</v>
       </c>
       <c r="G35" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.439768555147069e-41</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.06, 13.24, -1.32</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1504,14 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>9.84</v>
+        <v>14.04</v>
       </c>
       <c r="G36" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.624885406802116e-45</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>11.98, 13.15, -6.29</t>
         </is>
       </c>
     </row>
@@ -1534,14 +1534,14 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>9.84</v>
+        <v>29.22</v>
       </c>
       <c r="G37" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.875010938387574e-188</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.65, 21.84, 3.62</t>
         </is>
       </c>
     </row>
@@ -1564,14 +1564,14 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>9.84</v>
+        <v>13.98</v>
       </c>
       <c r="G38" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.08246973878258e-44</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.06, 13.24, -5.64</t>
         </is>
       </c>
     </row>
@@ -1594,14 +1594,14 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>9.84</v>
+        <v>13.44</v>
       </c>
       <c r="G39" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.785023554972823e-41</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.11, 13.29, -1.26</t>
         </is>
       </c>
     </row>
@@ -1624,14 +1624,14 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>9.84</v>
+        <v>13.49</v>
       </c>
       <c r="G40" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.196518685386608e-42</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.15, 13.34, -1.24</t>
         </is>
       </c>
     </row>
@@ -1654,14 +1654,14 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>9.84</v>
+        <v>14.05</v>
       </c>
       <c r="G41" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.785715567044263e-45</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.09, 13.26, -5.85</t>
         </is>
       </c>
     </row>
@@ -1684,14 +1684,14 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>9.84</v>
+        <v>29.92</v>
       </c>
       <c r="G42" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.815884050377117e-197</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.75, 22.34, 3.47</t>
         </is>
       </c>
     </row>
@@ -1714,14 +1714,14 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>9.84</v>
+        <v>13.68</v>
       </c>
       <c r="G43" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.377441099677514e-43</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.31, 13.53, -1.07</t>
         </is>
       </c>
     </row>
@@ -1744,14 +1744,14 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>9.84</v>
+        <v>13.66</v>
       </c>
       <c r="G44" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.917202945310766e-43</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.29, 13.5, -1.05</t>
         </is>
       </c>
     </row>
@@ -1774,14 +1774,14 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>9.84</v>
+        <v>13.95</v>
       </c>
       <c r="G45" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.581787807705562e-44</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.27, 13.48, -4.92</t>
         </is>
       </c>
     </row>
@@ -1804,14 +1804,14 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>9.84</v>
+        <v>13.9</v>
       </c>
       <c r="G46" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.326532056127628e-44</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.25, 13.46, -4.78</t>
         </is>
       </c>
     </row>
@@ -1834,14 +1834,14 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>9.84</v>
+        <v>13.85</v>
       </c>
       <c r="G47" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.939477887627076e-44</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.25, 13.45, -4.41</t>
         </is>
       </c>
     </row>
@@ -1864,14 +1864,14 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>9.84</v>
+        <v>13.46</v>
       </c>
       <c r="G48" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.32385696672101e-41</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.13, 13.31, -0.89</t>
         </is>
       </c>
     </row>
@@ -1894,14 +1894,14 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>9.84</v>
+        <v>13.73</v>
       </c>
       <c r="G49" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>3.476165481344158e-43</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.19, 13.38, -4.0</t>
         </is>
       </c>
     </row>
@@ -1924,14 +1924,14 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>9.84</v>
+        <v>13.59</v>
       </c>
       <c r="G50" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>2.369048323327631e-42</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.23, 13.43, -1.34</t>
         </is>
       </c>
     </row>
@@ -1954,14 +1954,14 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>9.84</v>
+        <v>13.45</v>
       </c>
       <c r="G51" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.481858553203805e-41</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>12.12, 13.29, -0.29</t>
         </is>
       </c>
     </row>
@@ -1984,14 +1984,14 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>9.84</v>
+        <v>28.86</v>
       </c>
       <c r="G52" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>1.783785948189318e-183</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.61, 21.47, 2.74</t>
         </is>
       </c>
     </row>
@@ -2014,14 +2014,14 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>9.84</v>
+        <v>24.43</v>
       </c>
       <c r="G53" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.245594704333063e-132</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.51, 21.04, 2.66</t>
         </is>
       </c>
     </row>
@@ -2044,14 +2044,14 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>9.84</v>
+        <v>23.63</v>
       </c>
       <c r="G54" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>9.683582716932677e-124</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.35, 20.37, 2.51</t>
         </is>
       </c>
     </row>
@@ -2074,14 +2074,14 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>9.84</v>
+        <v>28.75</v>
       </c>
       <c r="G55" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>5.159156067528768e-182</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.6, 21.4, 2.8</t>
         </is>
       </c>
     </row>
@@ -2104,14 +2104,14 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>9.84</v>
+        <v>22.45</v>
       </c>
       <c r="G56" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>6.398301328113765e-112</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>16.09, 19.49, 2.39</t>
         </is>
       </c>
     </row>
@@ -2134,14 +2134,14 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>9.84</v>
+        <v>21.32</v>
       </c>
       <c r="G57" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>4.034193157535672e-101</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>15.83, 18.73, 2.17</t>
         </is>
       </c>
     </row>
@@ -2164,14 +2164,14 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>9.84</v>
+        <v>19.24</v>
       </c>
       <c r="G58" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>8.210922229258382e-83</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>15.47, 17.89, 1.81</t>
         </is>
       </c>
     </row>
@@ -2194,14 +2194,14 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>9.84</v>
+        <v>21.18</v>
       </c>
       <c r="G59" t="n">
-        <v>3.822945287133192e-23</v>
+        <v>7.657157496743284e-100</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8.78, 9.55, -6.16</t>
+          <t>15.99, 19.11, 2.09</t>
         </is>
       </c>
     </row>
